--- a/상황근무개선검토_보고서.xlsx
+++ b/상황근무개선검토_보고서.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="보고서" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'보고서'!$A$1:$E$40</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'보고서'!$A$1:$E$42</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -44,11 +44,10 @@
     <font>
       <name val="맑은 고딕"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -57,16 +56,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F3864"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D9E1F2"/>
+        <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -89,6 +83,11 @@
       </bottom>
     </border>
     <border>
+      <bottom style="medium">
+        <color rgb="00000000"/>
+      </bottom>
+    </border>
+    <border>
       <left/>
       <right/>
       <top style="thin">
@@ -136,29 +135,33 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -524,7 +527,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E39"/>
+  <dimension ref="A1:E41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -541,433 +544,455 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>작성일: 2026-10-12   |   영업2본부 케이터링팀   |   작성: 이영진   |   수신: 본부장님</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>1. 검토 배경</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="n"/>
+    <row r="3" ht="18" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>작성일: 2026-10-12
+영업2본부 케이터링팀 / 이영진
+수신: 본부장님</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>담당</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>팀장</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>본부장</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="34" customHeight="1">
       <c r="C4" s="4" t="n"/>
       <c r="D4" s="4" t="n"/>
       <c r="E4" s="4" t="n"/>
     </row>
-    <row r="5" ht="44" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>1. 검토 배경</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n"/>
+      <c r="C6" s="6" t="n"/>
+      <c r="D6" s="6" t="n"/>
+      <c r="E6" s="6" t="n"/>
+    </row>
+    <row r="7" ht="44" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>토요일 오전까지 영업사원이 거래처 고충 전화를 받고, 일요일·공휴일에는 영업사원 1명이 당직으로 출고 상황을 처리하는 현재 구조에서, ① 영업지원 4명의 토요일 상황근무(오전~오후 2~3시) 도입과 ② 영업사원 일요일·공휴일 당직 운영 방식을 함께 검토 중이며, 팀원 의견을 모아 보고드립니다.</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>2. 현황</t>
         </is>
       </c>
-      <c r="B7" s="4" t="n"/>
-      <c r="C7" s="4" t="n"/>
-      <c r="D7" s="4" t="n"/>
-      <c r="E7" s="4" t="n"/>
-    </row>
-    <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="B9" s="6" t="n"/>
+      <c r="C9" s="6" t="n"/>
+      <c r="D9" s="6" t="n"/>
+      <c r="E9" s="6" t="n"/>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>구분</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B10" s="8" t="inlineStr">
         <is>
           <t>인원</t>
         </is>
       </c>
-      <c r="C8" s="7" t="n"/>
-      <c r="D8" s="6" t="inlineStr">
+      <c r="C10" s="9" t="n"/>
+      <c r="D10" s="8" t="inlineStr">
         <is>
           <t>현재 역할</t>
         </is>
       </c>
-      <c r="E8" s="7" t="n"/>
-    </row>
-    <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="8" t="inlineStr">
+      <c r="E10" s="9" t="n"/>
+    </row>
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="10" t="inlineStr">
         <is>
           <t>영업사원</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B11" s="10" t="inlineStr">
         <is>
           <t>5명</t>
         </is>
       </c>
-      <c r="C9" s="7" t="n"/>
-      <c r="D9" s="8" t="inlineStr">
+      <c r="C11" s="9" t="n"/>
+      <c r="D11" s="10" t="inlineStr">
         <is>
           <t>일요일·공휴일 당직(1명 출근, 나머지 휴무). 일요일에도 출고가 있어 상황 처리 필요</t>
         </is>
       </c>
-      <c r="E9" s="7" t="n"/>
-    </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="8" t="inlineStr"/>
-      <c r="B10" s="8" t="inlineStr"/>
-      <c r="C10" s="7" t="n"/>
-      <c r="D10" s="8" t="inlineStr">
+      <c r="E11" s="9" t="n"/>
+    </row>
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="10" t="inlineStr"/>
+      <c r="B12" s="10" t="inlineStr"/>
+      <c r="C12" s="9" t="n"/>
+      <c r="D12" s="10" t="inlineStr">
         <is>
           <t>토요일 오전까지 거래처 고충 전화 대응</t>
         </is>
       </c>
-      <c r="E10" s="7" t="n"/>
-    </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="E12" s="9" t="n"/>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="10" t="inlineStr">
         <is>
           <t>영업지원</t>
         </is>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B13" s="10" t="inlineStr">
         <is>
           <t>4명</t>
         </is>
       </c>
-      <c r="C11" s="7" t="n"/>
-      <c r="D11" s="8" t="inlineStr">
+      <c r="C13" s="9" t="n"/>
+      <c r="D13" s="10" t="inlineStr">
         <is>
           <t>주말 상황근무 없음</t>
         </is>
       </c>
-      <c r="E11" s="7" t="n"/>
-    </row>
-    <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="E13" s="9" t="n"/>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>3. 검토안</t>
         </is>
       </c>
-      <c r="B13" s="4" t="n"/>
-      <c r="C13" s="4" t="n"/>
-      <c r="D13" s="4" t="n"/>
-      <c r="E13" s="4" t="n"/>
-    </row>
-    <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="6" t="inlineStr">
+      <c r="B15" s="6" t="n"/>
+      <c r="C15" s="6" t="n"/>
+      <c r="D15" s="6" t="n"/>
+      <c r="E15" s="6" t="n"/>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="8" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="B14" s="7" t="n"/>
-      <c r="C14" s="6" t="inlineStr">
+      <c r="B16" s="9" t="n"/>
+      <c r="C16" s="8" t="inlineStr">
         <is>
           <t>현재</t>
         </is>
       </c>
-      <c r="D14" s="6" t="inlineStr">
+      <c r="D16" s="8" t="inlineStr">
         <is>
           <t>검토안</t>
         </is>
       </c>
-      <c r="E14" s="7" t="n"/>
-    </row>
-    <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="8" t="inlineStr">
+      <c r="E16" s="9" t="n"/>
+    </row>
+    <row r="17" ht="30" customHeight="1">
+      <c r="A17" s="10" t="inlineStr">
         <is>
           <t>토요일 (오전~오후 2~3시)</t>
         </is>
       </c>
-      <c r="B15" s="7" t="n"/>
-      <c r="C15" s="8" t="inlineStr">
+      <c r="B17" s="9" t="n"/>
+      <c r="C17" s="10" t="inlineStr">
         <is>
           <t>영업사원 오전까지 고충 전화 대응</t>
         </is>
       </c>
-      <c r="D15" s="8" t="inlineStr">
+      <c r="D17" s="10" t="inlineStr">
         <is>
           <t>영업지원 4명 출근, 상황 처리</t>
         </is>
       </c>
-      <c r="E15" s="7" t="n"/>
-    </row>
-    <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="8" t="inlineStr">
+      <c r="E17" s="9" t="n"/>
+    </row>
+    <row r="18" ht="30" customHeight="1">
+      <c r="A18" s="10" t="inlineStr">
         <is>
           <t>일요일·공휴일 당직</t>
         </is>
       </c>
-      <c r="B16" s="7" t="n"/>
-      <c r="C16" s="8" t="inlineStr">
+      <c r="B18" s="9" t="n"/>
+      <c r="C18" s="10" t="inlineStr">
         <is>
           <t>영업사원 1명 당직 (일요일 출고 상황 처리)</t>
         </is>
       </c>
-      <c r="D16" s="8" t="inlineStr">
+      <c r="D18" s="10" t="inlineStr">
         <is>
           <t>검토 대상: 당직 운영 방식(인원·순번·보상 등) 의견 취합 후 정리. 일요일 출고가 있어 상황 처리 기능은 유지 필요</t>
         </is>
       </c>
-      <c r="E16" s="7" t="n"/>
-    </row>
-    <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="8" t="inlineStr">
+      <c r="E18" s="9" t="n"/>
+    </row>
+    <row r="19" ht="30" customHeight="1">
+      <c r="A19" s="10" t="inlineStr">
         <is>
           <t>영업사원 부담</t>
         </is>
       </c>
-      <c r="B17" s="7" t="n"/>
-      <c r="C17" s="8" t="inlineStr">
+      <c r="B19" s="9" t="n"/>
+      <c r="C19" s="10" t="inlineStr">
         <is>
           <t>토요일 오전 전화 + 일요일·공휴일 당직</t>
         </is>
       </c>
-      <c r="D17" s="8" t="inlineStr">
+      <c r="D19" s="10" t="inlineStr">
         <is>
           <t>토요일 전화 부담 해소, 당직 부담은 의견 취합 후 조정 여부 검토</t>
         </is>
       </c>
-      <c r="E17" s="7" t="n"/>
-    </row>
-    <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="8" t="inlineStr">
+      <c r="E19" s="9" t="n"/>
+    </row>
+    <row r="20" ht="30" customHeight="1">
+      <c r="A20" s="10" t="inlineStr">
         <is>
           <t>세부 운영</t>
         </is>
       </c>
-      <c r="B18" s="7" t="n"/>
-      <c r="C18" s="8" t="inlineStr">
+      <c r="B20" s="9" t="n"/>
+      <c r="C20" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D18" s="8" t="inlineStr">
+      <c r="D20" s="10" t="inlineStr">
         <is>
           <t>출근 방식(4명 전원 / 순환), 대체휴무·수당은 의견 취합 후 확정</t>
         </is>
       </c>
-      <c r="E18" s="7" t="n"/>
-    </row>
-    <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="3" t="inlineStr">
+      <c r="E20" s="9" t="n"/>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="5" t="inlineStr">
         <is>
           <t>4. 팀원 의견 취합 (작성란)</t>
         </is>
       </c>
-      <c r="B20" s="4" t="n"/>
-      <c r="C20" s="4" t="n"/>
-      <c r="D20" s="4" t="n"/>
-      <c r="E20" s="4" t="n"/>
-    </row>
-    <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="6" t="inlineStr">
-        <is>
-          <t>구분</t>
-        </is>
-      </c>
-      <c r="B21" s="6" t="inlineStr">
-        <is>
-          <t>이름</t>
-        </is>
-      </c>
-      <c r="C21" s="6" t="inlineStr">
-        <is>
-          <t>토요일 상황근무 의견</t>
-        </is>
-      </c>
-      <c r="D21" s="6" t="inlineStr">
-        <is>
-          <t>일요일·공휴일 당직 의견</t>
-        </is>
-      </c>
-      <c r="E21" s="7" t="n"/>
-    </row>
-    <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="8" t="inlineStr">
-        <is>
-          <t>영업사원</t>
-        </is>
-      </c>
-      <c r="B22" s="8" t="inlineStr"/>
-      <c r="C22" s="8" t="inlineStr"/>
-      <c r="D22" s="8" t="inlineStr"/>
-      <c r="E22" s="7" t="n"/>
+      <c r="B22" s="6" t="n"/>
+      <c r="C22" s="6" t="n"/>
+      <c r="D22" s="6" t="n"/>
+      <c r="E22" s="6" t="n"/>
     </row>
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="8" t="inlineStr">
         <is>
+          <t>구분</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>이름</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="inlineStr">
+        <is>
+          <t>토요일 상황근무 의견</t>
+        </is>
+      </c>
+      <c r="D23" s="8" t="inlineStr">
+        <is>
+          <t>일요일·공휴일 당직 의견</t>
+        </is>
+      </c>
+      <c r="E23" s="9" t="n"/>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="10" t="inlineStr">
+        <is>
           <t>영업사원</t>
         </is>
       </c>
-      <c r="B23" s="8" t="inlineStr"/>
-      <c r="C23" s="8" t="inlineStr"/>
-      <c r="D23" s="8" t="inlineStr"/>
-      <c r="E23" s="7" t="n"/>
-    </row>
-    <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="8" t="inlineStr">
+      <c r="B24" s="10" t="inlineStr"/>
+      <c r="C24" s="10" t="inlineStr"/>
+      <c r="D24" s="10" t="inlineStr"/>
+      <c r="E24" s="9" t="n"/>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="10" t="inlineStr">
         <is>
           <t>영업사원</t>
         </is>
       </c>
-      <c r="B24" s="8" t="inlineStr"/>
-      <c r="C24" s="8" t="inlineStr"/>
-      <c r="D24" s="8" t="inlineStr"/>
-      <c r="E24" s="7" t="n"/>
-    </row>
-    <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="8" t="inlineStr">
+      <c r="B25" s="10" t="inlineStr"/>
+      <c r="C25" s="10" t="inlineStr"/>
+      <c r="D25" s="10" t="inlineStr"/>
+      <c r="E25" s="9" t="n"/>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="10" t="inlineStr">
         <is>
           <t>영업사원</t>
         </is>
       </c>
-      <c r="B25" s="8" t="inlineStr"/>
-      <c r="C25" s="8" t="inlineStr"/>
-      <c r="D25" s="8" t="inlineStr"/>
-      <c r="E25" s="7" t="n"/>
-    </row>
-    <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="8" t="inlineStr">
+      <c r="B26" s="10" t="inlineStr"/>
+      <c r="C26" s="10" t="inlineStr"/>
+      <c r="D26" s="10" t="inlineStr"/>
+      <c r="E26" s="9" t="n"/>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="10" t="inlineStr">
         <is>
           <t>영업사원</t>
         </is>
       </c>
-      <c r="B26" s="8" t="inlineStr"/>
-      <c r="C26" s="8" t="inlineStr"/>
-      <c r="D26" s="8" t="inlineStr"/>
-      <c r="E26" s="7" t="n"/>
-    </row>
-    <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="8" t="inlineStr">
+      <c r="B27" s="10" t="inlineStr"/>
+      <c r="C27" s="10" t="inlineStr"/>
+      <c r="D27" s="10" t="inlineStr"/>
+      <c r="E27" s="9" t="n"/>
+    </row>
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="10" t="inlineStr">
+        <is>
+          <t>영업사원</t>
+        </is>
+      </c>
+      <c r="B28" s="10" t="inlineStr"/>
+      <c r="C28" s="10" t="inlineStr"/>
+      <c r="D28" s="10" t="inlineStr"/>
+      <c r="E28" s="9" t="n"/>
+    </row>
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="10" t="inlineStr">
         <is>
           <t>영업지원</t>
         </is>
       </c>
-      <c r="B27" s="8" t="inlineStr"/>
-      <c r="C27" s="8" t="inlineStr"/>
-      <c r="D27" s="8" t="inlineStr"/>
-      <c r="E27" s="7" t="n"/>
-    </row>
-    <row r="28" ht="20" customHeight="1">
-      <c r="A28" s="8" t="inlineStr">
+      <c r="B29" s="10" t="inlineStr"/>
+      <c r="C29" s="10" t="inlineStr"/>
+      <c r="D29" s="10" t="inlineStr"/>
+      <c r="E29" s="9" t="n"/>
+    </row>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="10" t="inlineStr">
         <is>
           <t>영업지원</t>
         </is>
       </c>
-      <c r="B28" s="8" t="inlineStr"/>
-      <c r="C28" s="8" t="inlineStr"/>
-      <c r="D28" s="8" t="inlineStr"/>
-      <c r="E28" s="7" t="n"/>
-    </row>
-    <row r="29" ht="20" customHeight="1">
-      <c r="A29" s="8" t="inlineStr">
+      <c r="B30" s="10" t="inlineStr"/>
+      <c r="C30" s="10" t="inlineStr"/>
+      <c r="D30" s="10" t="inlineStr"/>
+      <c r="E30" s="9" t="n"/>
+    </row>
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="10" t="inlineStr">
         <is>
           <t>영업지원</t>
         </is>
       </c>
-      <c r="B29" s="8" t="inlineStr"/>
-      <c r="C29" s="8" t="inlineStr"/>
-      <c r="D29" s="8" t="inlineStr"/>
-      <c r="E29" s="7" t="n"/>
-    </row>
-    <row r="30" ht="20" customHeight="1">
-      <c r="A30" s="8" t="inlineStr">
+      <c r="B31" s="10" t="inlineStr"/>
+      <c r="C31" s="10" t="inlineStr"/>
+      <c r="D31" s="10" t="inlineStr"/>
+      <c r="E31" s="9" t="n"/>
+    </row>
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="10" t="inlineStr">
         <is>
           <t>영업지원</t>
         </is>
       </c>
-      <c r="B30" s="8" t="inlineStr"/>
-      <c r="C30" s="8" t="inlineStr"/>
-      <c r="D30" s="8" t="inlineStr"/>
-      <c r="E30" s="7" t="n"/>
-    </row>
-    <row r="32" ht="20" customHeight="1">
-      <c r="A32" s="3" t="inlineStr">
+      <c r="B32" s="10" t="inlineStr"/>
+      <c r="C32" s="10" t="inlineStr"/>
+      <c r="D32" s="10" t="inlineStr"/>
+      <c r="E32" s="9" t="n"/>
+    </row>
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" s="5" t="inlineStr">
         <is>
           <t>5. 장단점 및 쟁점</t>
         </is>
       </c>
-      <c r="B32" s="4" t="n"/>
-      <c r="C32" s="4" t="n"/>
-      <c r="D32" s="4" t="n"/>
-      <c r="E32" s="4" t="n"/>
-    </row>
-    <row r="33" ht="20" customHeight="1">
-      <c r="A33" s="6" t="inlineStr">
+      <c r="B34" s="6" t="n"/>
+      <c r="C34" s="6" t="n"/>
+      <c r="D34" s="6" t="n"/>
+      <c r="E34" s="6" t="n"/>
+    </row>
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="8" t="inlineStr">
         <is>
           <t>구분</t>
         </is>
       </c>
-      <c r="B33" s="7" t="n"/>
-      <c r="C33" s="6" t="inlineStr">
+      <c r="B35" s="9" t="n"/>
+      <c r="C35" s="8" t="inlineStr">
         <is>
           <t>내용</t>
         </is>
       </c>
-      <c r="D33" s="9" t="n"/>
-      <c r="E33" s="7" t="n"/>
-    </row>
-    <row r="34" ht="30" customHeight="1">
-      <c r="A34" s="8" t="inlineStr">
+      <c r="D35" s="11" t="n"/>
+      <c r="E35" s="9" t="n"/>
+    </row>
+    <row r="36" ht="30" customHeight="1">
+      <c r="A36" s="10" t="inlineStr">
         <is>
           <t>장점</t>
         </is>
       </c>
-      <c r="B34" s="7" t="n"/>
-      <c r="C34" s="8" t="inlineStr">
+      <c r="B36" s="9" t="n"/>
+      <c r="C36" s="10" t="inlineStr">
         <is>
           <t>영업사원의 토요일 대기 부담 해소, 사무실에서 자료 조회·지원 수월</t>
         </is>
       </c>
-      <c r="D34" s="9" t="n"/>
-      <c r="E34" s="7" t="n"/>
-    </row>
-    <row r="35" ht="30" customHeight="1">
-      <c r="A35" s="8" t="inlineStr">
+      <c r="D36" s="11" t="n"/>
+      <c r="E36" s="9" t="n"/>
+    </row>
+    <row r="37" ht="30" customHeight="1">
+      <c r="A37" s="10" t="inlineStr">
         <is>
           <t>단점</t>
         </is>
       </c>
-      <c r="B35" s="7" t="n"/>
-      <c r="C35" s="8" t="inlineStr">
+      <c r="B37" s="9" t="n"/>
+      <c r="C37" s="10" t="inlineStr">
         <is>
           <t>영업지원 주 6일 출근 부담, 4명 전원 출근 시 인력 낭비, 고객 상황 판단 권한·역량 문제</t>
         </is>
       </c>
-      <c r="D35" s="9" t="n"/>
-      <c r="E35" s="7" t="n"/>
-    </row>
-    <row r="36" ht="30" customHeight="1">
-      <c r="A36" s="8" t="inlineStr">
+      <c r="D37" s="11" t="n"/>
+      <c r="E37" s="9" t="n"/>
+    </row>
+    <row r="38" ht="30" customHeight="1">
+      <c r="A38" s="10" t="inlineStr">
         <is>
           <t>쟁점</t>
         </is>
       </c>
-      <c r="B36" s="7" t="n"/>
-      <c r="C36" s="8" t="inlineStr">
+      <c r="B38" s="9" t="n"/>
+      <c r="C38" s="10" t="inlineStr">
         <is>
           <t>토요일 출근 인원(전원/순환), 대체휴무·수당, 상황 건수·에스컬레이션 기준, 일요일·공휴일 당직 운영 방식(출고 대응 유지 전제)</t>
         </is>
       </c>
-      <c r="D36" s="9" t="n"/>
-      <c r="E36" s="7" t="n"/>
-    </row>
-    <row r="38" ht="20" customHeight="1">
-      <c r="A38" s="3" t="inlineStr">
+      <c r="D38" s="11" t="n"/>
+      <c r="E38" s="9" t="n"/>
+    </row>
+    <row r="40" ht="20" customHeight="1">
+      <c r="A40" s="5" t="inlineStr">
         <is>
           <t>6. 건의 사항</t>
         </is>
       </c>
-      <c r="B38" s="4" t="n"/>
-      <c r="C38" s="4" t="n"/>
-      <c r="D38" s="4" t="n"/>
-      <c r="E38" s="4" t="n"/>
-    </row>
-    <row r="39" ht="72" customHeight="1">
-      <c r="A39" s="5" t="inlineStr">
+      <c r="B40" s="6" t="n"/>
+      <c r="C40" s="6" t="n"/>
+      <c r="D40" s="6" t="n"/>
+      <c r="E40" s="6" t="n"/>
+    </row>
+    <row r="41" ht="72" customHeight="1">
+      <c r="A41" s="7" t="inlineStr">
         <is>
           <t>① 팀원 의견 취합 결과를 바탕으로 토요일 영업지원 상황근무 시범 운영 검토 (예: 1개월)
 ② 일요일·공휴일 영업사원 당직 운영 방식 개선 여부 함께 검토
@@ -978,52 +1003,52 @@
     </row>
   </sheetData>
   <mergeCells count="46">
-    <mergeCell ref="A39:E39"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="A34:E34"/>
     <mergeCell ref="D10:E10"/>
-    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A15:E15"/>
+    <mergeCell ref="D19:E19"/>
     <mergeCell ref="A36:B36"/>
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="B12:C12"/>
     <mergeCell ref="C36:E36"/>
     <mergeCell ref="A16:B16"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="A7:E7"/>
     <mergeCell ref="D11:E11"/>
+    <mergeCell ref="D13:E13"/>
     <mergeCell ref="D27:E27"/>
+    <mergeCell ref="A41:E41"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="D32:E32"/>
     <mergeCell ref="A18:B18"/>
-    <mergeCell ref="B8:C8"/>
     <mergeCell ref="D17:E17"/>
+    <mergeCell ref="C38:E38"/>
+    <mergeCell ref="B13:C13"/>
     <mergeCell ref="D16:E16"/>
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="C37:E37"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="D28:E28"/>
-    <mergeCell ref="A5:E5"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A32:E32"/>
     <mergeCell ref="D18:E18"/>
-    <mergeCell ref="B9:C9"/>
     <mergeCell ref="A17:B17"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="C34:E34"/>
+    <mergeCell ref="A22:E22"/>
+    <mergeCell ref="D12:E12"/>
     <mergeCell ref="A35:B35"/>
-    <mergeCell ref="D8:E8"/>
     <mergeCell ref="D25:E25"/>
-    <mergeCell ref="C33:E33"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="A20:E20"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A38:B38"/>
     <mergeCell ref="D24:E24"/>
     <mergeCell ref="D30:E30"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="A38:E38"/>
+    <mergeCell ref="A19:B19"/>
     <mergeCell ref="D29:E29"/>
     <mergeCell ref="D23:E23"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="A13:E13"/>
     <mergeCell ref="C35:E35"/>
     <mergeCell ref="D26:E26"/>
-    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="A40:E40"/>
+    <mergeCell ref="A9:E9"/>
+    <mergeCell ref="A3:B4"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
